--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N82_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N82_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>57.14745089343106</v>
+        <v>9.286460770182547</v>
       </c>
       <c r="D2" t="n">
-        <v>56.67200038647626</v>
+        <v>9.209200062802392</v>
       </c>
       <c r="E2" t="n">
-        <v>18.41619009922077</v>
+        <v>2.992630891123376</v>
       </c>
       <c r="F2" t="n">
-        <v>17.27191953861675</v>
+        <v>2.806686925025222</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>7.464188520159173</v>
+        <v>1.212930634525866</v>
       </c>
       <c r="D3" t="n">
-        <v>7.630559799476292</v>
+        <v>1.239965967414898</v>
       </c>
       <c r="E3" t="n">
-        <v>18.41619009922077</v>
+        <v>2.992630891123376</v>
       </c>
       <c r="F3" t="n">
-        <v>17.27191953861675</v>
+        <v>2.806686925025222</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>41.28425909958501</v>
+        <v>6.708692103682564</v>
       </c>
       <c r="D4" t="n">
-        <v>31.04354673534031</v>
+        <v>5.0445763444928</v>
       </c>
       <c r="E4" t="n">
-        <v>18.41619009922077</v>
+        <v>2.992630891123376</v>
       </c>
       <c r="F4" t="n">
-        <v>17.27191953861675</v>
+        <v>2.806686925025222</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>12.10724483639595</v>
+        <v>1.967427285914342</v>
       </c>
       <c r="D5" t="n">
-        <v>12.95445135543663</v>
+        <v>2.105098345258452</v>
       </c>
       <c r="E5" t="n">
-        <v>18.41619009922077</v>
+        <v>2.992630891123376</v>
       </c>
       <c r="F5" t="n">
-        <v>17.27191953861675</v>
+        <v>2.806686925025222</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>10.79464073684234</v>
+        <v>1.75412911973688</v>
       </c>
       <c r="D6" t="n">
-        <v>10.78817402608608</v>
+        <v>1.753078279238988</v>
       </c>
       <c r="E6" t="n">
-        <v>18.41619009922077</v>
+        <v>2.992630891123376</v>
       </c>
       <c r="F6" t="n">
-        <v>17.27191953861675</v>
+        <v>2.806686925025222</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>34.50016784549209</v>
+        <v>5.606277274892466</v>
       </c>
       <c r="D7" t="n">
-        <v>35.22800953995658</v>
+        <v>5.724551550242944</v>
       </c>
       <c r="E7" t="n">
-        <v>18.41619009922077</v>
+        <v>2.992630891123376</v>
       </c>
       <c r="F7" t="n">
-        <v>17.27191953861675</v>
+        <v>2.806686925025222</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
